--- a/data/trans_orig/IP19C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79991</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71639</t>
+          <t>71356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>78516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154312</t>
+          <t>154258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162191</t>
+          <t>162150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93906</t>
+          <t>93690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101652</t>
+          <t>101406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198576</t>
+          <t>198862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204294</t>
+          <t>204298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157574</t>
+          <t>157751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162853</t>
+          <t>162869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163031</t>
+          <t>162981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170996</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323036</t>
+          <t>323830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332588</t>
+          <t>332557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340926</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344655</t>
+          <t>344290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355122</t>
+          <t>354737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>689807</t>
+          <t>688969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702412</t>
+          <t>702151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69467</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74996</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>82416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89153</t>
+          <t>89137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155564</t>
+          <t>155203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163310</t>
+          <t>163351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120126</t>
+          <t>120022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123304</t>
+          <t>123658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130350</t>
+          <t>130349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246879</t>
+          <t>247335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254066</t>
+          <t>254059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137928</t>
+          <t>137803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143207</t>
+          <t>143206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>134042</t>
+          <t>134182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275325</t>
+          <t>275067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281573</t>
+          <t>281518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335439</t>
+          <t>334722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343937</t>
+          <t>343778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>348458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357450</t>
+          <t>357360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687756</t>
+          <t>687835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699842</t>
+          <t>699857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64347</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70927</t>
+          <t>71679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78358</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132830</t>
+          <t>132732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141883</t>
+          <t>142123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134095</t>
+          <t>134521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141276</t>
+          <t>141296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139063</t>
+          <t>139251</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276215</t>
+          <t>276694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284204</t>
+          <t>284251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133391</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124354</t>
+          <t>124377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130386</t>
+          <t>130381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260325</t>
+          <t>260275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267920</t>
+          <t>267912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332222</t>
+          <t>332429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342418</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340855</t>
+          <t>340852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>351497</t>
+          <t>351586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677919</t>
+          <t>678274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>691793</t>
+          <t>692042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C09-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8309</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4311</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9062</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75947</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72109</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78487</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>83085</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80197</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80024</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>75947</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71356</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78516</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>241</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154258</t>
+          <t>154413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162150</t>
+          <t>162239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1545</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5503</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105070</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102469</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>97648</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>93690</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>93679</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105070</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>101406</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>303</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198862</t>
+          <t>198653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204298</t>
+          <t>204295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2674</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10811</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2097</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5969</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167732</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171027</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>161400</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157751</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>162869</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157858</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>162867</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167732</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162981</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170963</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323830</t>
+          <t>323522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332557</t>
+          <t>333025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7123</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18017</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9353</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17441</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>350641</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>343714</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354608</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>515</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>346037</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>341599</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>348994</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>341577</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>348881</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,61%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>350641</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>344290</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>354737</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688969</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>702151</t>
+          <t>701995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2677</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2279</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2862</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86998</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82859</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89038</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73309</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68448</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75003</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68720</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86998</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>82416</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>89137</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>221</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155203</t>
+          <t>154576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163351</t>
+          <t>163352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89860</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89860</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89860</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6570</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3732</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7317</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128630</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124405</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130352</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>123089</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120022</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>120414</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>123754</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>128630</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>123658</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130349</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>361</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247335</t>
+          <t>247148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254059</t>
+          <t>254070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>130975</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>130975</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>130975</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>123754</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>123754</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>123754</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4839</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2083</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6010</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137614</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>134144</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138983</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>141730</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137803</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143206</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137581</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143204</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137614</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>134182</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>138983</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>406</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275067</t>
+          <t>275066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281518</t>
+          <t>281535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>138983</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>138983</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>138983</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>143813</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>143813</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>143813</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>138983</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>138983</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>138983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12686</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2675</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11731</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>12029</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>353911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347801</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>357541</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>340805</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>334722</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>343778</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336251</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>343974</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>353911</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348458</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357360</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687835</t>
+          <t>687569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699857</t>
+          <t>699531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>360487</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>346453</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>360487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8991</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2771</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7289</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7445</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8557</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75876</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71245</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78428</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>62361</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57843</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64359</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57687</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>64366</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>75876</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71679</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>78398</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132732</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142123</t>
+          <t>142504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80236</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80236</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80236</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65132</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65132</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65132</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80236</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80236</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4590</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8684</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8891</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4414</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>142300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138813</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>143665</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>138615</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>134521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141296</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>134314</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141476</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>142300</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>139251</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>143665</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276694</t>
+          <t>275625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284251</t>
+          <t>283947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143665</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143665</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>143205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>143205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>143205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143665</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143665</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7239</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1481</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5332</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6716</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128201</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123854</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130374</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136828</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132977</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133341</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>138309</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>128201</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>124377</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130381</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>369</t>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260275</t>
+          <t>260093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267912</t>
+          <t>267715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131093</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131093</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131093</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>138309</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>138309</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>138309</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131093</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131093</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131093</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>8842</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4889</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14753</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4151</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14237</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4692</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15426</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>347662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>341639</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>351914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>338340</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>332429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>342293</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>332945</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>343031</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347662</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>340852</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351586</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>678274</t>
+          <t>678478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>692042</t>
+          <t>692081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>356278</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>347182</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>356278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
